--- a/data/hr_employees_export_invalid.xlsx
+++ b/data/hr_employees_export_invalid.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>On leave</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">

--- a/data/hr_employees_export_invalid.xlsx
+++ b/data/hr_employees_export_invalid.xlsx
@@ -883,6 +883,11 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>EMP-1007</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
